--- a/EVO_1.2.1_Statistical_Toolkit.xlsx
+++ b/EVO_1.2.1_Statistical_Toolkit.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Confidence interval" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Z-score" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Same p different business" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Formula reference" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Activity 1.2.2 examples" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Formula reference" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -555,7 +556,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Hypothesis test — two-sample t-test with effect size and interval. Confidence interval — for a mean and for a proportion, plus a sample-size solver. Z-score — forwards and backwards, with tail probabilities. Two scenarios same p — the demonstration from the written solution. Formula reference — every formula in one place.</t>
+          <t>Hypothesis test — two-sample t-test with effect size and interval. Confidence interval — for a mean and for a proportion, plus a sample-size solver. Z-score — forwards and backwards, with tail probabilities. Two scenarios same p — the demonstration from the written solution. Activity 1.2.2 examples — the one-sample test against a claim and the pilot-study proportion, both live. Formula reference — every formula in one place.</t>
         </is>
       </c>
     </row>
@@ -1797,6 +1798,451 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Activity 1.2.2  ·  the two worked examples</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>A — ONE-SAMPLE TEST AGAINST A CLAIM  (Q8, the coffee chain)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>The chain claims customers rate it at least 4.5 out of 5. H0: mu &gt;= 4.5. Ha: mu &lt; 4.5. One-tailed, alpha set before the data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Claimed value  (mu0)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sample mean  (x-bar)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sample standard deviation  (s)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sample size  (n)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Significance level  (alpha)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Standard error</t>
+        </is>
+      </c>
+      <c r="B11" s="10">
+        <f>B8/SQRT(B9)</f>
+        <v/>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>= s / SQRT(n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Degrees of freedom</t>
+        </is>
+      </c>
+      <c r="B12" s="8">
+        <f>B9-1</f>
+        <v/>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>= n − 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>t statistic</t>
+        </is>
+      </c>
+      <c r="B13" s="9">
+        <f>(B7-B6)/B11</f>
+        <v/>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>= (x-bar − mu0) / SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>One-tailed p-value (lower)</t>
+        </is>
+      </c>
+      <c r="B14" s="10">
+        <f>T.DIST(B13,B12,TRUE)</f>
+        <v/>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>use T.DIST.RT for an upper-tail claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="B15" s="8">
+        <f>IF(B14&lt;B10,"REJECT H0 — the claim is not supported","FAIL TO REJECT — evidence insufficient, which is NOT the same as confirming the claim")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>t critical (two-tailed, 95%)</t>
+        </is>
+      </c>
+      <c r="B16" s="9">
+        <f>T.INV.2T(0.05,B12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>95% CI lower</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>B7-B16*B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>95% CI upper</t>
+        </is>
+      </c>
+      <c r="B18" s="9">
+        <f>B7+B16*B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Interval excludes the claim?</t>
+        </is>
+      </c>
+      <c r="B19" s="8">
+        <f>IF(OR(B18&lt;B6,B17&gt;B6),"YES — agrees with the test","NO — the claimed value is still plausible")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Cohen's d</t>
+        </is>
+      </c>
+      <c r="B20" s="9">
+        <f>(B6-B7)/B8</f>
+        <v/>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>= shortfall / s</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Effect size label</t>
+        </is>
+      </c>
+      <c r="B21" s="8">
+        <f>IF(ABS(B20)&lt;0.2,"below small",IF(ABS(B20)&lt;0.5,"small",IF(ABS(B20)&lt;0.8,"medium","large")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>READING BOTH TOGETHER: the claim is not defensible as stated, and the shortfall is a fifth of a standard deviation. Statistically established, practically minor — a compliance matter rather than a customer-experience crisis. Restating the claim costs almost nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>B — PROPORTION FROM A PILOT  (Q10, the 200-user product test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Proportion saying they would buy</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>124 of 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sample size</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Confidence level</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>z for this level</t>
+        </is>
+      </c>
+      <c r="B29" s="9">
+        <f>NORM.S.INV(1-(1-B28)/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Margin of error</t>
+        </is>
+      </c>
+      <c r="B30" s="10">
+        <f>B29*SQRT(B26*(1-B26)/B27)</f>
+        <v/>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>= z × SQRT( p(1−p) / n )</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Lower bound</t>
+        </is>
+      </c>
+      <c r="B31" s="15">
+        <f>B26-B30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Upper bound</t>
+        </is>
+      </c>
+      <c r="B32" s="15">
+        <f>B26+B30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Interval width in percentage points</t>
+        </is>
+      </c>
+      <c r="B33" s="14">
+        <f>(B32-B31)*100</f>
+        <v/>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>serviceable for go/no-go, far too vague to size a production run</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Intent is not purchase — convert before planning volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Share of stated intent that converts</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>varies by category; 0.3 to 0.6 is a common range</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Realistic demand, lower</t>
+        </is>
+      </c>
+      <c r="B37" s="15">
+        <f>B31*B36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Realistic demand, upper</t>
+        </is>
+      </c>
+      <c r="B38" s="15">
+        <f>B32*B36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Target margin for a volume decision</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>0.02 = ±2 percentage points</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sample needed for that margin</t>
+        </is>
+      </c>
+      <c r="B40" s="12">
+        <f>CEILING.MATH(B29^2*B26*(1-B26)/B39^2)</f>
+        <v/>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>= z² × p(1−p) / margin²</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="44" customHeight="1">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>WHAT NO SAMPLE SIZE FIXES: how the 200 were recruited. Enthusiasts, existing customers or a self-selected panel make this an inference from a favourable sample to a general market, and the interval will look narrow and be wrong. A pilot also gets attention a rollout cannot reproduce, so treat the figure as an upper bound rather than a forecast, and size the first production run from the lower end.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A23:C23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
